--- a/TP03CrmProj/TestData/TestScriptData.xlsx
+++ b/TP03CrmProj/TestData/TestScriptData.xlsx
@@ -3,18 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\OneDrive\Desktop\ProjectData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15030" windowHeight="6180"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>TC_ID</t>
   </si>
@@ -75,6 +71,9 @@
   </si>
   <si>
     <t>doc1_</t>
+  </si>
+  <si>
+    <t>Document name</t>
   </si>
 </sst>
 </file>
@@ -484,7 +483,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">

--- a/TP03CrmProj/TestData/TestScriptData.xlsx
+++ b/TP03CrmProj/TestData/TestScriptData.xlsx
@@ -28,9 +28,6 @@
     <t>TestcaseName</t>
   </si>
   <si>
-    <t>organizationName</t>
-  </si>
-  <si>
     <t>tc_01</t>
   </si>
   <si>
@@ -74,6 +71,9 @@
   </si>
   <si>
     <t>Document name</t>
+  </si>
+  <si>
+    <t>orgName</t>
   </si>
 </sst>
 </file>
@@ -417,18 +417,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -439,18 +439,18 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -461,18 +461,18 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -483,18 +483,18 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
         <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/TP03CrmProj/TestData/TestScriptData.xlsx
+++ b/TP03CrmProj/TestData/TestScriptData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiranmore/git/VTigerProjKiranM/TP03CrmProj/TestData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3C570C-DE5A-8246-AB57-53A3DAE26560}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B1DA13-2E19-F743-9B1B-611A6A5657E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="19640" windowHeight="9720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TP03CrmProj/TestData/TestScriptData.xlsx
+++ b/TP03CrmProj/TestData/TestScriptData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiranmore/git/VTigerProjKiranM/TP03CrmProj/TestData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72AD677-6B3F-D243-BD69-F6B049247D3B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A222BB7-3FCB-6E47-AF2D-3933D200D89C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="19640" windowHeight="9720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>TC_ID</t>
   </si>
@@ -91,6 +91,18 @@
   </si>
   <si>
     <t>Oppor_</t>
+  </si>
+  <si>
+    <t>tc_06</t>
+  </si>
+  <si>
+    <t>createLeadTest</t>
+  </si>
+  <si>
+    <t>company name</t>
+  </si>
+  <si>
+    <t>Apple_</t>
   </si>
 </sst>
 </file>
@@ -415,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
@@ -536,6 +548,28 @@
         <v>21</v>
       </c>
     </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TP03CrmProj/TestData/TestScriptData.xlsx
+++ b/TP03CrmProj/TestData/TestScriptData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>TC_ID</t>
   </si>
@@ -74,6 +74,18 @@
   </si>
   <si>
     <t>ProductName</t>
+  </si>
+  <si>
+    <t>tc_06</t>
+  </si>
+  <si>
+    <t>createInvoiceTest</t>
+  </si>
+  <si>
+    <t>InvName</t>
+  </si>
+  <si>
+    <t>invoice01_</t>
   </si>
 </sst>
 </file>
@@ -398,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
@@ -497,6 +509,28 @@
         <v>12</v>
       </c>
     </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TP03CrmProj/TestData/TestScriptData.xlsx
+++ b/TP03CrmProj/TestData/TestScriptData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>TC_ID</t>
   </si>
@@ -74,18 +74,6 @@
   </si>
   <si>
     <t>ProductName</t>
-  </si>
-  <si>
-    <t>tc_06</t>
-  </si>
-  <si>
-    <t>createInvoiceTest</t>
-  </si>
-  <si>
-    <t>InvName</t>
-  </si>
-  <si>
-    <t>invoice01_</t>
   </si>
 </sst>
 </file>
@@ -509,28 +497,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-    </row>
+    <row r="16" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TP03CrmProj/TestData/TestScriptData.xlsx
+++ b/TP03CrmProj/TestData/TestScriptData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19770" windowHeight="6180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15030" windowHeight="6180"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <si>
     <t>TC_ID</t>
   </si>
@@ -76,7 +76,40 @@
     <t>ProductName</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>tc_05</t>
+  </si>
+  <si>
+    <t>tc_06</t>
+  </si>
+  <si>
+    <t>tc_07</t>
+  </si>
+  <si>
+    <t>Opp_</t>
+  </si>
+  <si>
+    <t>OppName</t>
+  </si>
+  <si>
+    <t>InvName</t>
+  </si>
+  <si>
+    <t>invoice01_</t>
+  </si>
+  <si>
+    <t>createLeadTest</t>
+  </si>
+  <si>
+    <t>createInvoiceTest</t>
+  </si>
+  <si>
+    <t>createOpportunityTest</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Apple_</t>
   </si>
 </sst>
 </file>
@@ -401,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
@@ -500,13 +533,72 @@
         <v>12</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TP03CrmProj/TestData/TestScriptData.xlsx
+++ b/TP03CrmProj/TestData/TestScriptData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiranmore/git/VTigerProjKiranM/TP03CrmProj/TestData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE05A030-C2E6-E74E-AE52-C23988240419}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA4B988-9A05-C244-9AFE-6B08F0EA7678}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="18060" windowHeight="11060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>TC_ID</t>
   </si>
@@ -112,6 +112,18 @@
   </si>
   <si>
     <t>Apple_</t>
+  </si>
+  <si>
+    <t>tc_08</t>
+  </si>
+  <si>
+    <t>creatTroubleTicket</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>ticket_</t>
   </si>
 </sst>
 </file>
@@ -436,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
@@ -601,6 +613,28 @@
         <v>28</v>
       </c>
     </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TP03CrmProj/TestData/TestScriptData.xlsx
+++ b/TP03CrmProj/TestData/TestScriptData.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiranmore/git/VTigerProjKiranM/TP03CrmProj/TestData/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FA8BCD-60E0-354A-ABF2-5959F7758AE5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="18060" windowHeight="11060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15030" windowHeight="6180"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
   <si>
     <t>TC_ID</t>
   </si>
@@ -127,12 +122,24 @@
   </si>
   <si>
     <t>Company</t>
+  </si>
+  <si>
+    <t>tc_09</t>
+  </si>
+  <si>
+    <t>salesOrder</t>
+  </si>
+  <si>
+    <t>sales_</t>
+  </si>
+  <si>
+    <t>Subject</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -450,19 +457,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,7 +480,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -484,7 +491,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +502,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -506,7 +513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,7 +524,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -528,7 +535,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,7 +546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -550,7 +557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,7 +568,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -572,7 +579,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,7 +590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -594,7 +601,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -605,7 +612,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -616,7 +623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -627,7 +634,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -636,6 +643,28 @@
       </c>
       <c r="C23" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/TP03CrmProj/TestData/TestScriptData.xlsx
+++ b/TP03CrmProj/TestData/TestScriptData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiranmore/git/VTigerProjKiranM/TP03CrmProj/TestData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C09D8A-5A29-D044-A03C-82A30927CB70}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528442A1-2617-7F47-93E2-66A17EFE7655}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="18060" windowHeight="11060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
